--- a/Game/Floor.xlsx
+++ b/Game/Floor.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Steam\steamapps\common\Elin\Package\_Lang_Vietnamese\Lang\VN\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746F8677-E8CC-4B52-A302-025D506C99FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B987444E-E602-48BF-8DEF-3618331AFB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Floor" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Floor!$A$2:$H$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Floor!$A$2:$H$139</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="335">
   <si>
     <t>id</t>
   </si>
@@ -52,784 +52,829 @@
     <t>0</t>
   </si>
   <si>
+    <t>EA 23.295</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>solid soil floor</t>
+  </si>
+  <si>
+    <t>固い土の床</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Editor Floor(Interior)</t>
+  </si>
+  <si>
+    <t>特殊フロア(室内)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Editor Floor(Exterior)</t>
+  </si>
+  <si>
+    <t>特殊フロア(野外)</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>field</t>
+  </si>
+  <si>
+    <t>畑</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>plank floor</t>
+  </si>
+  <si>
+    <t>板の床</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>stone floor</t>
+  </si>
+  <si>
+    <t>石の床</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>carpet</t>
+  </si>
+  <si>
+    <t>カーペット</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>support floor</t>
+  </si>
+  <si>
+    <t>足場の床</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>glass floor</t>
+  </si>
+  <si>
+    <t>硝子の床</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>mirror floor</t>
+  </si>
+  <si>
+    <t>鏡の床</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>rusty metal floor</t>
+  </si>
+  <si>
+    <t>錆びた金属の床</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>metal floor</t>
+  </si>
+  <si>
+    <t>金属の床</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>magma</t>
+  </si>
+  <si>
+    <t>マグマの床</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>log floor</t>
+  </si>
+  <si>
+    <t>丸太の床</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>crystal floor</t>
+  </si>
+  <si>
+    <t>結晶の床</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>tile floor</t>
+  </si>
+  <si>
+    <t>タイルの床</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>brick floor</t>
+  </si>
+  <si>
+    <t>煉瓦の床</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>sand floor</t>
+  </si>
+  <si>
+    <t>砂床</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>砂の床</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>lawn floor</t>
+  </si>
+  <si>
+    <t>芝生の床</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>thick grass floor</t>
+  </si>
+  <si>
+    <t>茂みの床</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>straw floor</t>
+  </si>
+  <si>
+    <t>藁の床</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>smooth soil floor</t>
+  </si>
+  <si>
+    <t>滑らかな土の床</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>ice floor</t>
+  </si>
+  <si>
+    <t>氷の床</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>snow floor</t>
+  </si>
+  <si>
+    <t>雪の床</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>soil floor</t>
+  </si>
+  <si>
+    <t>土の床</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>wooden floor</t>
+  </si>
+  <si>
+    <t>大木の床</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>deep grass floor</t>
+  </si>
+  <si>
+    <t>深い茂みの床</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>shallow water</t>
+  </si>
+  <si>
+    <t>浅い水</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>いかだの床</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>ash floor</t>
+  </si>
+  <si>
+    <t>焼け焦げた床</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>modern floor</t>
+  </si>
+  <si>
+    <t>モダンな床</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>pedestal</t>
+  </si>
+  <si>
+    <t>ペデスタル</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>deep water</t>
+  </si>
+  <si>
+    <t>深い水</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>very shallow water</t>
+  </si>
+  <si>
+    <t>とても浅い水</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>grass floor</t>
+  </si>
+  <si>
+    <t>草の床</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>quality plank floor</t>
+  </si>
+  <si>
+    <t>上質板の床</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Editor Floor(Transparent)</t>
+  </si>
+  <si>
+    <t>特殊フロア(透明)</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>modern carpet</t>
+  </si>
+  <si>
+    <t>モダンなカーペット</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>plank pattern floor</t>
+  </si>
+  <si>
+    <t>木模様の床</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Editor Floor(Sky)</t>
+  </si>
+  <si>
+    <t>特殊フロア(空)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Tatami</t>
+  </si>
+  <si>
+    <t>畳</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>wooden grille floor</t>
+  </si>
+  <si>
+    <t>格子板の床</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>metal grille floor</t>
+  </si>
+  <si>
+    <t>金属格子の床</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>cave floor</t>
+  </si>
+  <si>
+    <t>洞窟の床</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>barren soil floor</t>
+  </si>
+  <si>
+    <t>荒地の床</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>橋</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>bush floor</t>
+  </si>
+  <si>
+    <t>草むらの床</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>red algae floor</t>
+  </si>
+  <si>
+    <t>紅藻の床</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>seabed floor</t>
+  </si>
+  <si>
+    <t>海底の床</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>chocolate floor</t>
+  </si>
+  <si>
+    <t>チョコレートの床</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>biscuit floor</t>
+  </si>
+  <si>
+    <t>ビスケットの床</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>mushroom floor</t>
+  </si>
+  <si>
+    <t>キノコの床</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>cloud floor</t>
+  </si>
+  <si>
+    <t>雲の床</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>alien floor</t>
+  </si>
+  <si>
+    <t>エイリアンの床</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>stage floor</t>
+  </si>
+  <si>
+    <t>ステージの床</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Alpha 11.1</t>
+  </si>
+  <si>
+    <t>Alpha 19.1</t>
+  </si>
+  <si>
+    <t>Alpha 20.66</t>
+  </si>
+  <si>
+    <t>Alpha 20.7</t>
+  </si>
+  <si>
+    <t>Alpha 12.1</t>
+  </si>
+  <si>
+    <t>Alpha 14.1</t>
+  </si>
+  <si>
+    <t>Alpha 20.27</t>
+  </si>
+  <si>
+    <t>Alpha 20.40</t>
+  </si>
+  <si>
+    <t>Alpha 20.51</t>
+  </si>
+  <si>
+    <t>Alpha 20.69</t>
+  </si>
+  <si>
+    <t>Alpha 20.70</t>
+  </si>
+  <si>
+    <t>Alpha 21.0</t>
+  </si>
+  <si>
+    <t>Beta 22.13</t>
+  </si>
+  <si>
+    <t>Beta 22.22</t>
+  </si>
+  <si>
+    <t>Beta 22.57</t>
+  </si>
+  <si>
+    <t>EA 23.143</t>
+  </si>
+  <si>
+    <t>EA 23.145</t>
+  </si>
+  <si>
+    <t>EA 23.168</t>
+  </si>
+  <si>
+    <t>EA 23.169</t>
+  </si>
+  <si>
+    <t>EA 23.188 Patch 2</t>
+  </si>
+  <si>
+    <t>EA 23.247 Patch 1</t>
+  </si>
+  <si>
     <t>EA 23.267 Patch 1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>solid soil floor</t>
-  </si>
-  <si>
-    <t>固い土の床</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Editor Floor(Interior)</t>
-  </si>
-  <si>
-    <t>特殊フロア(室内)</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Editor Floor(Exterior)</t>
-  </si>
-  <si>
-    <t>特殊フロア(野外)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>field</t>
-  </si>
-  <si>
-    <t>畑</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>plank floor</t>
-  </si>
-  <si>
-    <t>板の床</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>stone floor</t>
-  </si>
-  <si>
-    <t>石の床</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>carpet</t>
-  </si>
-  <si>
-    <t>カーペット</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>support floor</t>
-  </si>
-  <si>
-    <t>足場の床</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>glass floor</t>
-  </si>
-  <si>
-    <t>硝子の床</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>mirror floor</t>
-  </si>
-  <si>
-    <t>鏡の床</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>rusty metal floor</t>
-  </si>
-  <si>
-    <t>錆びた金属の床</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>metal floor</t>
-  </si>
-  <si>
-    <t>金属の床</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>magma</t>
-  </si>
-  <si>
-    <t>マグマの床</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>log floor</t>
-  </si>
-  <si>
-    <t>丸太の床</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>crystal floor</t>
-  </si>
-  <si>
-    <t>結晶の床</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>tile floor</t>
-  </si>
-  <si>
-    <t>タイルの床</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>brick floor</t>
-  </si>
-  <si>
-    <t>煉瓦の床</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>sand floor</t>
-  </si>
-  <si>
-    <t>砂床</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>砂の床</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>lawn floor</t>
-  </si>
-  <si>
-    <t>芝生の床</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>thick grass floor</t>
-  </si>
-  <si>
-    <t>茂みの床</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>straw floor</t>
-  </si>
-  <si>
-    <t>藁の床</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>smooth soil floor</t>
-  </si>
-  <si>
-    <t>滑らかな土の床</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>ice floor</t>
-  </si>
-  <si>
-    <t>氷の床</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>snow floor</t>
-  </si>
-  <si>
-    <t>雪の床</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>soil floor</t>
-  </si>
-  <si>
-    <t>土の床</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>wooden floor</t>
-  </si>
-  <si>
-    <t>大木の床</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>deep grass floor</t>
-  </si>
-  <si>
-    <t>深い茂みの床</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>shallow water</t>
-  </si>
-  <si>
-    <t>浅い水</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>いかだの床</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>ash floor</t>
-  </si>
-  <si>
-    <t>焼け焦げた床</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>modern floor</t>
-  </si>
-  <si>
-    <t>モダンな床</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>pedestal</t>
-  </si>
-  <si>
-    <t>ペデスタル</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>deep water</t>
-  </si>
-  <si>
-    <t>深い水</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>very shallow water</t>
-  </si>
-  <si>
-    <t>とても浅い水</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>grass floor</t>
-  </si>
-  <si>
-    <t>草の床</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>quality plank floor</t>
-  </si>
-  <si>
-    <t>上質板の床</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>Editor Floor(Transparent)</t>
-  </si>
-  <si>
-    <t>特殊フロア(透明)</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>modern carpet</t>
-  </si>
-  <si>
-    <t>モダンなカーペット</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>plank pattern floor</t>
-  </si>
-  <si>
-    <t>木模様の床</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>Editor Floor(Sky)</t>
-  </si>
-  <si>
-    <t>特殊フロア(空)</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>Tatami</t>
-  </si>
-  <si>
-    <t>畳</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>wooden grille floor</t>
-  </si>
-  <si>
-    <t>格子板の床</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>metal grille floor</t>
-  </si>
-  <si>
-    <t>金属格子の床</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>cave floor</t>
-  </si>
-  <si>
-    <t>洞窟の床</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>barren soil floor</t>
-  </si>
-  <si>
-    <t>荒地の床</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>bridge</t>
-  </si>
-  <si>
-    <t>橋</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>bush floor</t>
-  </si>
-  <si>
-    <t>草むらの床</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>red algae floor</t>
-  </si>
-  <si>
-    <t>紅藻の床</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>seabed floor</t>
-  </si>
-  <si>
-    <t>海底の床</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>chocolate floor</t>
-  </si>
-  <si>
-    <t>チョコレートの床</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>biscuit floor</t>
-  </si>
-  <si>
-    <t>ビスケットの床</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>mushroom floor</t>
-  </si>
-  <si>
-    <t>キノコの床</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Alpha 11.1</t>
-  </si>
-  <si>
-    <t>Alpha 19.1</t>
-  </si>
-  <si>
-    <t>Alpha 20.66</t>
-  </si>
-  <si>
-    <t>Alpha 20.7</t>
-  </si>
-  <si>
-    <t>Alpha 12.1</t>
-  </si>
-  <si>
-    <t>Alpha 14.1</t>
-  </si>
-  <si>
-    <t>Alpha 20.27</t>
-  </si>
-  <si>
-    <t>Alpha 20.40</t>
-  </si>
-  <si>
-    <t>Alpha 20.51</t>
-  </si>
-  <si>
-    <t>Alpha 20.69</t>
-  </si>
-  <si>
-    <t>Alpha 20.70</t>
-  </si>
-  <si>
-    <t>Alpha 21.0</t>
-  </si>
-  <si>
-    <t>Beta 22.13</t>
-  </si>
-  <si>
-    <t>Beta 22.22</t>
-  </si>
-  <si>
-    <t>Beta 22.57</t>
-  </si>
-  <si>
-    <t>EA 23.143</t>
-  </si>
-  <si>
-    <t>EA 23.145</t>
-  </si>
-  <si>
-    <t>EA 23.168</t>
-  </si>
-  <si>
-    <t>EA 23.169</t>
-  </si>
-  <si>
-    <t>EA 23.188 Patch 2</t>
-  </si>
-  <si>
-    <t>EA 23.247 Patch 1</t>
+    <t>EA 23.287 Patch 4</t>
   </si>
   <si>
     <t>sàn đất cứng</t>
   </si>
   <si>
-    <t>Sàn đặc biệt (trong nhà)</t>
-  </si>
-  <si>
-    <t>Sàn đặc biệt (ngoài trời)</t>
+    <t>sàn đặc biệt (trong nhà)</t>
+  </si>
+  <si>
+    <t>sàn đặc biệt (ngoài trời)</t>
   </si>
   <si>
     <t>ruộng</t>
@@ -974,6 +1019,15 @@
   </si>
   <si>
     <t>sàn nấm</t>
+  </si>
+  <si>
+    <t>sàn mây</t>
+  </si>
+  <si>
+    <t>sàn alien</t>
+  </si>
+  <si>
+    <t>sàn sân khấu</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="16" customWidth="1" collapsed="1"/>
@@ -1368,7 +1422,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1376,10 +1430,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1393,10 +1447,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1410,10 +1464,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C6" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1427,10 +1481,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1444,10 +1498,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1461,10 +1515,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1478,10 +1532,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1495,10 +1549,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1512,10 +1566,10 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C12" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
@@ -1529,10 +1583,10 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C13" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -1546,10 +1600,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C14" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
@@ -1563,10 +1617,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -1580,10 +1634,10 @@
         <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C16" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -1597,10 +1651,10 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C17" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -1614,10 +1668,10 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C18" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1631,10 +1685,10 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -1648,10 +1702,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="D20" t="s">
         <v>47</v>
@@ -1665,10 +1719,10 @@
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C21" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
@@ -1682,10 +1736,10 @@
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -1699,10 +1753,10 @@
         <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -1716,10 +1770,10 @@
         <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="D24" t="s">
         <v>57</v>
@@ -1733,10 +1787,10 @@
         <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
@@ -1750,10 +1804,10 @@
         <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C26" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -1767,10 +1821,10 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -1784,10 +1838,10 @@
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C28" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D28" t="s">
         <v>29</v>
@@ -1801,10 +1855,10 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C29" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -1818,10 +1872,10 @@
         <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C30" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D30" t="s">
         <v>69</v>
@@ -1835,10 +1889,10 @@
         <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -1852,10 +1906,10 @@
         <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C32" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -1869,10 +1923,10 @@
         <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C33" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
@@ -1886,10 +1940,10 @@
         <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C34" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -1903,10 +1957,10 @@
         <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C35" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
@@ -1920,10 +1974,10 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C36" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -1937,10 +1991,10 @@
         <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="D37" t="s">
         <v>81</v>
@@ -1954,10 +2008,10 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C38" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="D38" t="s">
         <v>84</v>
@@ -1971,10 +2025,10 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C39" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="D39" t="s">
         <v>87</v>
@@ -1988,10 +2042,10 @@
         <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C40" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -2005,10 +2059,10 @@
         <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
@@ -2022,10 +2076,10 @@
         <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D42" t="s">
         <v>96</v>
@@ -2039,10 +2093,10 @@
         <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C43" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D43" t="s">
         <v>99</v>
@@ -2056,10 +2110,10 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C44" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="D44" t="s">
         <v>102</v>
@@ -2073,10 +2127,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C45" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D45" t="s">
         <v>105</v>
@@ -2090,10 +2144,10 @@
         <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C46" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="D46" t="s">
         <v>108</v>
@@ -2107,10 +2161,10 @@
         <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C47" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="D47" t="s">
         <v>111</v>
@@ -2124,10 +2178,10 @@
         <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C48" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D48" t="s">
         <v>102</v>
@@ -2141,10 +2195,10 @@
         <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C49" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -2158,10 +2212,10 @@
         <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C50" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
@@ -2175,10 +2229,10 @@
         <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C51" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D51" t="s">
         <v>69</v>
@@ -2192,10 +2246,10 @@
         <v>118</v>
       </c>
       <c r="B52" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C52" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="D52" t="s">
         <v>119</v>
@@ -2209,10 +2263,10 @@
         <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C53" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="D53" t="s">
         <v>122</v>
@@ -2226,10 +2280,10 @@
         <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C54" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="D54" t="s">
         <v>122</v>
@@ -2243,10 +2297,10 @@
         <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C55" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
@@ -2260,10 +2314,10 @@
         <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C56" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
@@ -2277,10 +2331,10 @@
         <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D57" t="s">
         <v>128</v>
@@ -2294,10 +2348,10 @@
         <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C58" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -2311,10 +2365,10 @@
         <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C59" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
@@ -2328,10 +2382,10 @@
         <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C60" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
@@ -2345,10 +2399,10 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C61" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D61" t="s">
         <v>69</v>
@@ -2362,10 +2416,10 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C62" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
@@ -2379,10 +2433,10 @@
         <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C63" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D63" t="s">
         <v>29</v>
@@ -2396,10 +2450,10 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C64" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
@@ -2413,10 +2467,10 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D65" t="s">
         <v>29</v>
@@ -2430,10 +2484,10 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C66" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
@@ -2447,10 +2501,10 @@
         <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C67" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -2464,10 +2518,10 @@
         <v>140</v>
       </c>
       <c r="B68" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C68" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
@@ -2481,10 +2535,10 @@
         <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C69" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D69" t="s">
         <v>63</v>
@@ -2498,10 +2552,10 @@
         <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C70" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D70" t="s">
         <v>63</v>
@@ -2515,10 +2569,10 @@
         <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C71" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D71" t="s">
         <v>63</v>
@@ -2532,10 +2586,10 @@
         <v>144</v>
       </c>
       <c r="B72" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D72" t="s">
         <v>63</v>
@@ -2549,10 +2603,10 @@
         <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C73" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D73" t="s">
         <v>63</v>
@@ -2566,10 +2620,10 @@
         <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C74" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -2583,10 +2637,10 @@
         <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C75" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D75" t="s">
         <v>148</v>
@@ -2600,10 +2654,10 @@
         <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C76" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="D76" t="s">
         <v>151</v>
@@ -2617,10 +2671,10 @@
         <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C77" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D77" t="s">
         <v>74</v>
@@ -2634,10 +2688,10 @@
         <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C78" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="D78" t="s">
         <v>155</v>
@@ -2651,10 +2705,10 @@
         <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C79" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="D79" t="s">
         <v>158</v>
@@ -2668,10 +2722,10 @@
         <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C80" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D80" t="s">
         <v>161</v>
@@ -2685,10 +2739,10 @@
         <v>163</v>
       </c>
       <c r="B81" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C81" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="D81" t="s">
         <v>164</v>
@@ -2702,10 +2756,10 @@
         <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="D82" t="s">
         <v>164</v>
@@ -2719,10 +2773,10 @@
         <v>167</v>
       </c>
       <c r="B83" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C83" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="D83" t="s">
         <v>164</v>
@@ -2736,10 +2790,10 @@
         <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C84" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="D84" t="s">
         <v>164</v>
@@ -2753,10 +2807,10 @@
         <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C85" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D85" t="s">
         <v>170</v>
@@ -2770,10 +2824,10 @@
         <v>172</v>
       </c>
       <c r="B86" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C86" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D86" t="s">
         <v>170</v>
@@ -2787,10 +2841,10 @@
         <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C87" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D87" t="s">
         <v>170</v>
@@ -2804,10 +2858,10 @@
         <v>174</v>
       </c>
       <c r="B88" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D88" t="s">
         <v>170</v>
@@ -2821,10 +2875,10 @@
         <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C89" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D89" t="s">
         <v>170</v>
@@ -2838,10 +2892,10 @@
         <v>176</v>
       </c>
       <c r="B90" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C90" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D90" t="s">
         <v>170</v>
@@ -2855,10 +2909,10 @@
         <v>177</v>
       </c>
       <c r="B91" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C91" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D91" t="s">
         <v>170</v>
@@ -2872,10 +2926,10 @@
         <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C92" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D92" t="s">
         <v>170</v>
@@ -2889,10 +2943,10 @@
         <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C93" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D93" t="s">
         <v>180</v>
@@ -2906,10 +2960,10 @@
         <v>182</v>
       </c>
       <c r="B94" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C94" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D94" t="s">
         <v>63</v>
@@ -2923,10 +2977,10 @@
         <v>183</v>
       </c>
       <c r="B95" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="D95" t="s">
         <v>164</v>
@@ -2940,10 +2994,10 @@
         <v>184</v>
       </c>
       <c r="B96" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="D96" t="s">
         <v>185</v>
@@ -2957,10 +3011,10 @@
         <v>187</v>
       </c>
       <c r="B97" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D97" t="s">
         <v>188</v>
@@ -2974,10 +3028,10 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D98" t="s">
         <v>188</v>
@@ -2991,10 +3045,10 @@
         <v>191</v>
       </c>
       <c r="B99" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="D99" t="s">
         <v>192</v>
@@ -3008,10 +3062,10 @@
         <v>194</v>
       </c>
       <c r="B100" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C100" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="D100" t="s">
         <v>192</v>
@@ -3025,10 +3079,10 @@
         <v>195</v>
       </c>
       <c r="B101" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C101" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="D101" t="s">
         <v>185</v>
@@ -3042,10 +3096,10 @@
         <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C102" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="D102" t="s">
         <v>197</v>
@@ -3059,10 +3113,10 @@
         <v>199</v>
       </c>
       <c r="B103" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C103" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="D103" t="s">
         <v>200</v>
@@ -3076,10 +3130,10 @@
         <v>202</v>
       </c>
       <c r="B104" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C104" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="D104" t="s">
         <v>155</v>
@@ -3093,10 +3147,10 @@
         <v>203</v>
       </c>
       <c r="B105" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C105" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D105" t="s">
         <v>69</v>
@@ -3110,10 +3164,10 @@
         <v>204</v>
       </c>
       <c r="B106" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C106" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D106" t="s">
         <v>69</v>
@@ -3127,10 +3181,10 @@
         <v>205</v>
       </c>
       <c r="B107" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C107" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D107" t="s">
         <v>128</v>
@@ -3144,10 +3198,10 @@
         <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C108" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D108" t="s">
         <v>29</v>
@@ -3161,10 +3215,10 @@
         <v>207</v>
       </c>
       <c r="B109" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C109" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -3178,10 +3232,10 @@
         <v>208</v>
       </c>
       <c r="B110" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C110" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D110" t="s">
         <v>63</v>
@@ -3195,10 +3249,10 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C111" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -3212,10 +3266,10 @@
         <v>210</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C112" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
@@ -3229,10 +3283,10 @@
         <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C113" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D113" t="s">
         <v>63</v>
@@ -3246,10 +3300,10 @@
         <v>212</v>
       </c>
       <c r="B114" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C114" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D114" t="s">
         <v>63</v>
@@ -3263,10 +3317,10 @@
         <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C115" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="D115" t="s">
         <v>214</v>
@@ -3280,10 +3334,10 @@
         <v>216</v>
       </c>
       <c r="B116" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C116" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="D116" t="s">
         <v>217</v>
@@ -3297,10 +3351,10 @@
         <v>219</v>
       </c>
       <c r="B117" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C117" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="D117" t="s">
         <v>217</v>
@@ -3314,10 +3368,10 @@
         <v>220</v>
       </c>
       <c r="B118" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C118" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D118" t="s">
         <v>50</v>
@@ -3331,10 +3385,10 @@
         <v>221</v>
       </c>
       <c r="B119" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C119" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D119" t="s">
         <v>50</v>
@@ -3348,10 +3402,10 @@
         <v>222</v>
       </c>
       <c r="B120" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C120" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -3365,10 +3419,10 @@
         <v>223</v>
       </c>
       <c r="B121" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C121" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D121" t="s">
         <v>50</v>
@@ -3382,10 +3436,10 @@
         <v>224</v>
       </c>
       <c r="B122" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C122" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D122" t="s">
         <v>50</v>
@@ -3399,10 +3453,10 @@
         <v>225</v>
       </c>
       <c r="B123" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C123" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D123" t="s">
         <v>50</v>
@@ -3416,10 +3470,10 @@
         <v>226</v>
       </c>
       <c r="B124" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C124" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="D124" t="s">
         <v>227</v>
@@ -3433,10 +3487,10 @@
         <v>229</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C125" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D125" t="s">
         <v>230</v>
@@ -3450,10 +3504,10 @@
         <v>232</v>
       </c>
       <c r="B126" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C126" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="D126" t="s">
         <v>233</v>
@@ -3467,10 +3521,10 @@
         <v>235</v>
       </c>
       <c r="B127" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C127" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="D127" t="s">
         <v>236</v>
@@ -3484,10 +3538,10 @@
         <v>238</v>
       </c>
       <c r="B128" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C128" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="D128" t="s">
         <v>239</v>
@@ -3501,10 +3555,10 @@
         <v>241</v>
       </c>
       <c r="B129" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C129" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="D129" t="s">
         <v>239</v>
@@ -3518,10 +3572,10 @@
         <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C130" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D130" t="s">
         <v>26</v>
@@ -3535,10 +3589,10 @@
         <v>243</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>279</v>
       </c>
       <c r="C131" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D131" t="s">
         <v>26</v>
@@ -3552,10 +3606,10 @@
         <v>244</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>279</v>
       </c>
       <c r="C132" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D132" t="s">
         <v>26</v>
@@ -3564,8 +3618,127 @@
         <v>27</v>
       </c>
     </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>245</v>
+      </c>
+      <c r="B133" t="s">
+        <v>280</v>
+      </c>
+      <c r="C133" t="s">
+        <v>332</v>
+      </c>
+      <c r="D133" t="s">
+        <v>246</v>
+      </c>
+      <c r="E133" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>248</v>
+      </c>
+      <c r="B134" t="s">
+        <v>280</v>
+      </c>
+      <c r="C134" t="s">
+        <v>333</v>
+      </c>
+      <c r="D134" t="s">
+        <v>249</v>
+      </c>
+      <c r="E134" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" t="s">
+        <v>334</v>
+      </c>
+      <c r="D135" t="s">
+        <v>252</v>
+      </c>
+      <c r="E135" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>254</v>
+      </c>
+      <c r="B136" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" t="s">
+        <v>334</v>
+      </c>
+      <c r="D136" t="s">
+        <v>252</v>
+      </c>
+      <c r="E136" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>255</v>
+      </c>
+      <c r="B137" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" t="s">
+        <v>333</v>
+      </c>
+      <c r="D137" t="s">
+        <v>249</v>
+      </c>
+      <c r="E137" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>256</v>
+      </c>
+      <c r="B138" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" t="s">
+        <v>333</v>
+      </c>
+      <c r="D138" t="s">
+        <v>249</v>
+      </c>
+      <c r="E138" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>257</v>
+      </c>
+      <c r="B139" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" t="s">
+        <v>333</v>
+      </c>
+      <c r="D139" t="s">
+        <v>249</v>
+      </c>
+      <c r="E139" t="s">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:H132" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:H139" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>